--- a/nr-update-valueset/ig/StructureDefinition-as-dr-device.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:32:05+00:00</t>
+    <t>2024-03-06T16:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-update-valueset/ig/StructureDefinition-as-dr-device.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-dr-device.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -695,6 +695,195 @@
     <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS).</t>
   </si>
   <si>
+    <t>Device.identifier:numAutorisationArhgos.id</t>
+  </si>
+  <si>
+    <t>Device.identifier.id</t>
+  </si>
+  <si>
+    <t>Device.identifier:numAutorisationArhgos.extension</t>
+  </si>
+  <si>
+    <t>Device.identifier.extension</t>
+  </si>
+  <si>
+    <t>Device.identifier:numAutorisationArhgos.use</t>
+  </si>
+  <si>
+    <t>Device.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Device.identifier:numAutorisationArhgos.type</t>
+  </si>
+  <si>
+    <t>Device.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>Device.identifier:numAutorisationArhgos.system</t>
+  </si>
+  <si>
+    <t>Device.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>https://arhgos.ars.sante.fr/</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Device.identifier:numAutorisationArhgos.value</t>
+  </si>
+  <si>
+    <t>Device.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Device.identifier:numAutorisationArhgos.period</t>
+  </si>
+  <si>
+    <t>Device.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Device.identifier:numAutorisationArhgos.assigner</t>
+  </si>
+  <si>
+    <t>Device.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>Device.definition</t>
   </si>
   <si>
@@ -709,10 +898,6 @@
   </si>
   <si>
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
@@ -892,9 +1077,6 @@
     <t>Supports a way to distinguish hand entered from machine read data.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes to identify how UDI data was entered.</t>
   </si>
   <si>
@@ -929,10 +1111,6 @@
   </si>
   <si>
     <t>Device.statusReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>online | paused | standby | offline | not-ready | transduc-discon | hw-discon | off</t>
@@ -1727,7 +1905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM78"/>
+  <dimension ref="A1:AM86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.01171875" customWidth="true" bestFit="true"/>
@@ -1749,7 +1927,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -4223,7 +4401,7 @@
         <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4234,7 +4412,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -4246,17 +4424,15 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>218</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4305,7 +4481,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>103</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4314,13 +4490,13 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>222</v>
+        <v>76</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
@@ -4331,21 +4507,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -4354,19 +4530,19 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4404,19 +4580,19 @@
         <v>76</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4428,13 +4604,13 @@
         <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>76</v>
@@ -4442,10 +4618,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4462,22 +4638,26 @@
         <v>76</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>101</v>
+        <v>223</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
       </c>
@@ -4501,13 +4681,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4525,7 +4705,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4534,13 +4714,13 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>104</v>
+        <v>231</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4551,21 +4731,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4574,21 +4754,23 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>108</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>109</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
@@ -4612,46 +4794,46 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>76</v>
+        <v>239</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4662,45 +4844,45 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4710,10 +4892,10 @@
         <v>76</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>76</v>
@@ -4749,22 +4931,22 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>98</v>
+        <v>251</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4775,14 +4957,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>238</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4804,13 +4986,13 @@
         <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4824,7 +5006,7 @@
         <v>76</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>76</v>
+        <v>257</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>76</v>
@@ -4860,7 +5042,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4875,25 +5057,25 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>244</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>246</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4909,19 +5091,19 @@
         <v>76</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4971,7 +5153,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4983,24 +5165,24 @@
         <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>251</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5020,23 +5202,21 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
@@ -5084,7 +5264,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5096,10 +5276,10 @@
         <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -5110,21 +5290,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>258</v>
+        <v>76</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -5133,19 +5313,19 @@
         <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5195,7 +5375,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5207,35 +5387,35 @@
         <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>263</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5247,16 +5427,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>100</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5306,13 +5486,13 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>96</v>
@@ -5321,21 +5501,21 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>76</v>
+        <v>212</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>269</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5358,20 +5538,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
       </c>
@@ -5395,13 +5571,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>274</v>
+        <v>76</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>276</v>
+        <v>76</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5419,7 +5595,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>103</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5428,13 +5604,13 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>277</v>
+        <v>104</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5445,42 +5621,42 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>109</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>281</v>
+        <v>110</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5506,49 +5682,49 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>274</v>
+        <v>76</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>282</v>
+        <v>76</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>283</v>
+        <v>76</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>114</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>284</v>
+        <v>98</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>76</v>
@@ -5556,44 +5732,46 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>287</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
       </c>
@@ -5617,13 +5795,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>291</v>
+        <v>76</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>292</v>
+        <v>76</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5641,7 +5819,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5653,13 +5831,13 @@
         <v>96</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>293</v>
+        <v>98</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -5667,21 +5845,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
@@ -5690,19 +5868,19 @@
         <v>76</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>100</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5752,7 +5930,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5767,25 +5945,25 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>76</v>
+        <v>306</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5795,7 +5973,7 @@
         <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>76</v>
@@ -5804,16 +5982,16 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>241</v>
+        <v>309</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5863,7 +6041,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5878,21 +6056,21 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>98</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5903,7 +6081,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -5915,16 +6093,20 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>306</v>
+        <v>133</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
       </c>
@@ -5972,7 +6154,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5987,32 +6169,32 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>310</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>76</v>
+        <v>318</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -6021,18 +6203,20 @@
         <v>76</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -6081,7 +6265,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6096,32 +6280,32 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>76</v>
+        <v>325</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6130,19 +6314,19 @@
         <v>76</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>100</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6192,7 +6376,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6207,21 +6391,21 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>300</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6235,7 +6419,7 @@
         <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>76</v>
@@ -6244,18 +6428,20 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
@@ -6279,13 +6465,13 @@
         <v>76</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>76</v>
+        <v>335</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>76</v>
@@ -6303,7 +6489,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6318,10 +6504,10 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6329,10 +6515,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6343,27 +6529,29 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6388,13 +6576,13 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6412,13 +6600,13 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>96</v>
@@ -6427,10 +6615,10 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>104</v>
+        <v>343</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>76</v>
+        <v>344</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6438,10 +6626,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6452,7 +6640,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -6464,15 +6652,17 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>101</v>
+        <v>346</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6497,13 +6687,13 @@
         <v>76</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>76</v>
+        <v>349</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>76</v>
+        <v>350</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>76</v>
@@ -6521,25 +6711,25 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>103</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>104</v>
+        <v>351</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>76</v>
+        <v>344</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>76</v>
@@ -6547,21 +6737,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>106</v>
+        <v>353</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6573,16 +6763,16 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>108</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>109</v>
+        <v>355</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>110</v>
+        <v>356</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6620,84 +6810,82 @@
         <v>76</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>114</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>98</v>
+        <v>357</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>76</v>
+        <v>303</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>76</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>235</v>
+        <v>361</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
       </c>
@@ -6745,47 +6933,47 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>236</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>331</v>
+        <v>76</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -6797,17 +6985,15 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>100</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6856,10 +7042,10 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>84</v>
@@ -6871,21 +7057,21 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>104</v>
+        <v>367</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>76</v>
+        <v>303</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>76</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6893,10 +7079,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6908,17 +7094,15 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>168</v>
+        <v>364</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6943,13 +7127,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>274</v>
+        <v>76</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>337</v>
+        <v>76</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>338</v>
+        <v>76</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6967,10 +7151,10 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>84</v>
@@ -6982,21 +7166,21 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>76</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7022,13 +7206,13 @@
         <v>100</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7078,7 +7262,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7093,21 +7277,21 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>76</v>
+        <v>358</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7118,10 +7302,10 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>76</v>
@@ -7133,13 +7317,13 @@
         <v>100</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>322</v>
+        <v>380</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7189,7 +7373,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7204,10 +7388,10 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>323</v>
+        <v>381</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>76</v>
@@ -7215,10 +7399,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7229,10 +7413,10 @@
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>76</v>
@@ -7241,17 +7425,15 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7276,11 +7458,13 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>350</v>
+        <v>76</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>76</v>
@@ -7298,13 +7482,13 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>96</v>
@@ -7313,7 +7497,7 @@
         <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>293</v>
+        <v>104</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7324,10 +7508,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7338,7 +7522,7 @@
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7350,13 +7534,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>352</v>
+        <v>101</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>353</v>
+        <v>102</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7407,19 +7591,19 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>351</v>
+        <v>103</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>104</v>
@@ -7433,21 +7617,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>76</v>
@@ -7459,15 +7643,17 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7504,34 +7690,34 @@
         <v>76</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7542,14 +7728,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7562,24 +7748,26 @@
         <v>76</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>109</v>
+        <v>295</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
       </c>
@@ -7615,19 +7803,19 @@
         <v>76</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>114</v>
+        <v>296</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7653,46 +7841,44 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>233</v>
+        <v>389</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>234</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>235</v>
+        <v>391</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
       </c>
@@ -7740,22 +7926,22 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>236</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7766,14 +7952,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>331</v>
+        <v>76</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7792,16 +7978,16 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>287</v>
+        <v>168</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7827,13 +8013,13 @@
         <v>76</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>76</v>
+        <v>395</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>76</v>
+        <v>396</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>76</v>
@@ -7851,7 +8037,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -7866,10 +8052,10 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>293</v>
+        <v>397</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>76</v>
+        <v>303</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>76</v>
@@ -7877,10 +8063,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7891,7 +8077,7 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
@@ -7906,13 +8092,13 @@
         <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7962,7 +8148,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7977,10 +8163,10 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>104</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>76</v>
@@ -7988,10 +8174,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8014,15 +8200,17 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8071,13 +8259,13 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>96</v>
@@ -8086,10 +8274,10 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>104</v>
+        <v>381</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>76</v>
+        <v>303</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>76</v>
@@ -8097,10 +8285,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8114,7 +8302,7 @@
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>76</v>
@@ -8123,15 +8311,17 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8156,13 +8346,11 @@
         <v>76</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>76</v>
+        <v>408</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>76</v>
@@ -8180,7 +8368,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>103</v>
+        <v>405</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8189,13 +8377,13 @@
         <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>104</v>
+        <v>351</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -8206,21 +8394,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>76</v>
@@ -8232,17 +8420,15 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>285</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>108</v>
+        <v>410</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8279,19 +8465,19 @@
         <v>76</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>114</v>
+        <v>409</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8303,10 +8489,10 @@
         <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8317,46 +8503,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>234</v>
+        <v>101</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>76</v>
       </c>
@@ -8404,22 +8586,22 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>236</v>
+        <v>103</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8430,21 +8612,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>331</v>
+        <v>106</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>76</v>
@@ -8456,16 +8638,16 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>287</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>370</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>371</v>
+        <v>109</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>290</v>
+        <v>110</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8503,34 +8685,34 @@
         <v>76</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>369</v>
+        <v>114</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>293</v>
+        <v>98</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8541,42 +8723,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>373</v>
+        <v>294</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>76</v>
       </c>
@@ -8624,25 +8810,25 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>372</v>
+        <v>296</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>375</v>
+        <v>98</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>76</v>
@@ -8650,14 +8836,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>76</v>
+        <v>389</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8676,16 +8862,16 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>241</v>
+        <v>348</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8735,7 +8921,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -8750,7 +8936,7 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>104</v>
+        <v>351</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>76</v>
@@ -8761,10 +8947,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8775,7 +8961,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>76</v>
@@ -8787,15 +8973,17 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8844,13 +9032,13 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>96</v>
@@ -8862,7 +9050,7 @@
         <v>104</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>76</v>
+        <v>303</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8870,10 +9058,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8884,7 +9072,7 @@
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>76</v>
@@ -8896,13 +9084,13 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>100</v>
+        <v>285</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>101</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>102</v>
+        <v>423</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8953,19 +9141,19 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>103</v>
+        <v>421</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>104</v>
@@ -8979,21 +9167,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>76</v>
@@ -9005,17 +9193,15 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9052,34 +9238,34 @@
         <v>76</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
@@ -9090,14 +9276,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>233</v>
+        <v>106</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9110,26 +9296,24 @@
         <v>76</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>234</v>
+        <v>108</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O67" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>76</v>
       </c>
@@ -9165,19 +9349,19 @@
         <v>76</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9203,44 +9387,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>287</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>386</v>
+        <v>294</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>387</v>
+        <v>295</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
       </c>
@@ -9288,22 +9474,22 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>385</v>
+        <v>296</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>293</v>
+        <v>98</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9314,21 +9500,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>76</v>
+        <v>389</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>76</v>
@@ -9340,16 +9526,16 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>389</v>
+        <v>234</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9399,22 +9585,22 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>393</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
@@ -9425,10 +9611,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9439,7 +9625,7 @@
         <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>76</v>
@@ -9451,17 +9637,15 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>287</v>
+        <v>205</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9510,13 +9694,13 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>96</v>
@@ -9525,10 +9709,10 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>293</v>
+        <v>433</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>76</v>
+        <v>303</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>76</v>
@@ -9536,10 +9720,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9547,10 +9731,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>76</v>
@@ -9562,20 +9746,18 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>399</v>
+        <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>401</v>
+        <v>436</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>76</v>
       </c>
@@ -9623,10 +9805,10 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>84</v>
@@ -9635,13 +9817,13 @@
         <v>96</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>403</v>
+        <v>104</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>404</v>
+        <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>76</v>
@@ -9649,10 +9831,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9663,10 +9845,10 @@
         <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>76</v>
@@ -9675,17 +9857,15 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>406</v>
+        <v>285</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -9734,25 +9914,25 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>409</v>
+        <v>104</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>410</v>
+        <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>76</v>
@@ -9760,10 +9940,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9774,7 +9954,7 @@
         <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>76</v>
@@ -9786,17 +9966,15 @@
         <v>76</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>412</v>
+        <v>100</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -9845,25 +10023,25 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>411</v>
+        <v>103</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>416</v>
+        <v>76</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>417</v>
+        <v>104</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>410</v>
+        <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>76</v>
@@ -9871,21 +10049,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>76</v>
@@ -9897,20 +10075,18 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>420</v>
+        <v>108</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>421</v>
+        <v>109</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>76</v>
       </c>
@@ -9946,37 +10122,37 @@
         <v>76</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>418</v>
+        <v>114</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>423</v>
+        <v>98</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>424</v>
+        <v>76</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>76</v>
@@ -9984,44 +10160,46 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>426</v>
+        <v>294</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>427</v>
+        <v>295</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>76</v>
       </c>
@@ -10069,25 +10247,25 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>429</v>
+        <v>98</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>424</v>
+        <v>76</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>76</v>
@@ -10095,10 +10273,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10106,10 +10284,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>76</v>
@@ -10121,16 +10299,16 @@
         <v>76</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>431</v>
+        <v>234</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>434</v>
+        <v>348</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10180,13 +10358,13 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>96</v>
@@ -10195,7 +10373,7 @@
         <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>435</v>
+        <v>351</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>76</v>
@@ -10206,10 +10384,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10220,7 +10398,7 @@
         <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>76</v>
@@ -10229,19 +10407,19 @@
         <v>76</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>287</v>
+        <v>447</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>290</v>
+        <v>450</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10291,7 +10469,7 @@
         <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10303,10 +10481,10 @@
         <v>96</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>97</v>
+        <v>451</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>277</v>
+        <v>452</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>76</v>
@@ -10317,10 +10495,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10331,7 +10509,7 @@
         <v>77</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>76</v>
@@ -10343,16 +10521,16 @@
         <v>76</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>440</v>
+        <v>234</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>221</v>
+        <v>348</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10402,32 +10580,924 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>223</v>
+        <v>351</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM78">
+  <autoFilter ref="A1:AM86">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10437,7 +11507,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-valueset/ig/StructureDefinition-as-dr-device.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
